--- a/tests/realSuite/Piano-viaggi_TENNIS-TAVOLO-IC_con-vettore-e-cel_24-nov-25/input.xlsx
+++ b/tests/realSuite/Piano-viaggi_TENNIS-TAVOLO-IC_con-vettore-e-cel_24-nov-25/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,27 +451,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IC AVIO</t>
+          <t>IC ALDENO - MATTARELLO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Avio, Via Degasperi 69</t>
+          <t>Mattarello, Via Torre Franca (fermata bus “al parco”)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IC CLES</t>
+          <t>IC AVIO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cles, Piazza Fiera</t>
+          <t>Avio, Via Degasperi 69</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -481,42 +481,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IC FONDO</t>
+          <t>IC CLES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Borgo d'Anaunia Via Laviosa Zambotti - Fondo, 24</t>
+          <t>Cles, Piazza Fiera</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO PAGANELLA</t>
+          <t>IC FONDO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mezzolombardo, Via Degli Alpini, 17</t>
+          <t>Borgo d'Anaunia Via Laviosa Zambotti - Fondo, 24</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IC PERGINE 1</t>
+          <t>IC MEZZOLOMBARDO PAGANELLA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pergine Valsugana, Via dei Caduti 39</t>
+          <t>Mezzolombardo, Via Degli Alpini, 17</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -526,12 +526,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IC ROVERETO EST</t>
+          <t>IC PERGINE 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rovereto, Piazzale Orsi Fermata corriere davanti IPIA VERONESI</t>
+          <t>Pergine Valsugana, Via dei Caduti 39</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -541,15 +541,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>IC ROVERETO EST</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rovereto, Piazzale Orsi Fermata corriere davanti IPIA VERONESI</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>IC VALLE DEI LAGHI – DRO</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Dro, Via S Antonio, 17</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C10" t="n">
         <v>9</v>
       </c>
     </row>

--- a/tests/realSuite/Piano-viaggi_TENNIS-TAVOLO-IC_con-vettore-e-cel_24-nov-25/input.xlsx
+++ b/tests/realSuite/Piano-viaggi_TENNIS-TAVOLO-IC_con-vettore-e-cel_24-nov-25/input.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aldeno, Fermata via Filzi</t>
+          <t>Scuola Secondaria di Primo Grado "Antonio Fogazzaro", 1, Via della Torre Franca, Regole, Mattarello di Sopra, Mattarello, Trento, Territorio Val d'Adige, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38123, Italia</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -456,7 +456,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mattarello, Via Torre Franca (fermata bus “al parco”)</t>
+          <t>Scuola Secondaria di Primo Grado "Antonio Fogazzaro", 1, Via della Torre Franca, Regole, Mattarello di Sopra, Mattarello, Trento, Territorio Val d'Adige, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38123, Italia</t>
         </is>
       </c>
       <c r="C3" t="n">
